--- a/datasets/tenant-inputs/generated/meridian-health/standard-2026-07-v3/core-dimensions/02_org_ownership.xlsx
+++ b/datasets/tenant-inputs/generated/meridian-health/standard-2026-07-v3/core-dimensions/02_org_ownership.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start Here" sheetId="1" r:id="R6f112c2fba944272"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Client Intake" sheetId="2" r:id="R98fa0979ab504880"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Questionnaire" sheetId="3" r:id="R228db943842b41de"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Examples" sheetId="4" r:id="R6d83d2a58a324c6c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference Values" sheetId="5" r:id="R1598cb1eb58b4a1d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationship Expectations" sheetId="6" r:id="R6ad7c1087c724e37"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start Here" sheetId="1" r:id="R98731308ece241bc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Client Intake" sheetId="2" r:id="Rcf72a95867404d26"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Questionnaire" sheetId="3" r:id="Rf1bff585af7046ae"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Examples" sheetId="4" r:id="R25bbfc2352374e9c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference Values" sheetId="5" r:id="R17367863a9334331"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationship Expectations" sheetId="6" r:id="R2bee9e9720284ed6"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -624,7 +624,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcfe75f2098734452"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R042b1b74c2484479"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -785,7 +785,7 @@
         <x:v>Executive Office SME lead; data steward; technology owner</x:v>
       </x:c>
       <x:c r="M6" s="78" t="str">
-        <x:v>Named people and approval thresholds require client confirmation.</x:v>
+        <x:v>Validate Corporate strategy office (record 1) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for org ownership.</x:v>
       </x:c>
       <x:c r="N6" s="41" t="str">
         <x:v>High</x:v>
@@ -829,7 +829,7 @@
         <x:v>Provider Operations SME lead; data steward; technology owner</x:v>
       </x:c>
       <x:c r="M7" s="79" t="str">
-        <x:v>Named people and approval thresholds require client confirmation.</x:v>
+        <x:v>Confirm Clinical operations leadership (record 2) current-vs-target status, module boundary, volume baseline, and relationship links before this org ownership record is used downstream.</x:v>
       </x:c>
       <x:c r="N7" s="45" t="str">
         <x:v>High</x:v>
@@ -873,7 +873,7 @@
         <x:v>Claims Operations SME lead; data steward; technology owner</x:v>
       </x:c>
       <x:c r="M8" t="str">
-        <x:v>Named people and approval thresholds require client confirmation.</x:v>
+        <x:v>Attach client evidence for Claims operations leadership (record 3), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="N8" t="str">
         <x:v>High</x:v>
@@ -917,7 +917,7 @@
         <x:v>Eligibility and Benefits SME lead; data steward; technology owner</x:v>
       </x:c>
       <x:c r="M9" t="str">
-        <x:v>Named people and approval thresholds require client confirmation.</x:v>
+        <x:v>Reconcile Benefits operations team (record 4) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="N9" t="str">
         <x:v>High</x:v>
@@ -961,7 +961,7 @@
         <x:v>Prior Authorization and UM SME lead; data steward; technology owner</x:v>
       </x:c>
       <x:c r="M10" t="str">
-        <x:v>Named people and approval thresholds require client confirmation.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for UM operations team (record 5) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="N10" t="str">
         <x:v>Medium</x:v>
@@ -1005,7 +1005,7 @@
         <x:v>Contact Center and Member Service SME lead; data steward; technology owner</x:v>
       </x:c>
       <x:c r="M11" t="str">
-        <x:v>Named people and approval thresholds require client confirmation.</x:v>
+        <x:v>Validate Member service operations (record 6) against Agent Assist / Member Service evidence: stale knowledge article duplicates; confirm human-approved next-best-action workflow owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="N11" t="str">
         <x:v>High</x:v>
@@ -1049,7 +1049,7 @@
         <x:v>Revenue Cycle Operations SME lead; data steward; technology owner</x:v>
       </x:c>
       <x:c r="M12" t="str">
-        <x:v>Named people and approval thresholds require client confirmation.</x:v>
+        <x:v>Confirm Revenue cycle leadership (record 7) current-vs-target status, module boundary, volume baseline, and relationship links before this org ownership record is used downstream.</x:v>
       </x:c>
       <x:c r="N12" t="str">
         <x:v>High</x:v>
@@ -1093,7 +1093,7 @@
         <x:v>Finance Analytics SME lead; data steward; technology owner</x:v>
       </x:c>
       <x:c r="M13" t="str">
-        <x:v>Named people and approval thresholds require client confirmation.</x:v>
+        <x:v>Validate Finance analytics team (record 8) against Finance Analytics evidence: slow close-window dashboards; confirm vendor master harmonization owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="N13" t="str">
         <x:v>High</x:v>
@@ -1137,7 +1137,7 @@
         <x:v>Workforce Analytics SME lead; data steward; technology owner</x:v>
       </x:c>
       <x:c r="M14" t="str">
-        <x:v>Named people and approval thresholds require client confirmation.</x:v>
+        <x:v>Reconcile Workforce analytics office (record 9) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="N14" t="str">
         <x:v>High</x:v>
@@ -1181,7 +1181,7 @@
         <x:v>Clinical Quality Analytics SME lead; data steward; technology owner</x:v>
       </x:c>
       <x:c r="M15" t="str">
-        <x:v>Named people and approval thresholds require client confirmation.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Quality analytics team (record 10) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="N15" t="str">
         <x:v>Medium</x:v>
@@ -1225,7 +1225,7 @@
         <x:v>Claims and Payment Analytics SME lead; data steward; technology owner</x:v>
       </x:c>
       <x:c r="M16" t="str">
-        <x:v>Named people and approval thresholds require client confirmation.</x:v>
+        <x:v>Validate Claims analytics group (record 11) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for org ownership.</x:v>
       </x:c>
       <x:c r="N16" t="str">
         <x:v>High</x:v>
@@ -1269,7 +1269,7 @@
         <x:v>Provider Performance Analytics SME lead; data steward; technology owner</x:v>
       </x:c>
       <x:c r="M17" t="str">
-        <x:v>Named people and approval thresholds require client confirmation.</x:v>
+        <x:v>Confirm Provider performance team (record 12) current-vs-target status, module boundary, volume baseline, and relationship links before this org ownership record is used downstream.</x:v>
       </x:c>
       <x:c r="N17" t="str">
         <x:v>High</x:v>
@@ -1313,7 +1313,7 @@
         <x:v>Enterprise Data Platform SME lead; data steward; technology owner</x:v>
       </x:c>
       <x:c r="M18" t="str">
-        <x:v>Named people and approval thresholds require client confirmation.</x:v>
+        <x:v>Attach client evidence for Enterprise data platform team (record 13), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="N18" t="str">
         <x:v>High</x:v>
@@ -1357,7 +1357,7 @@
         <x:v>Data Governance and Data Quality SME lead; data steward; technology owner</x:v>
       </x:c>
       <x:c r="M19" t="str">
-        <x:v>Named people and approval thresholds require client confirmation.</x:v>
+        <x:v>Reconcile Data governance council (record 14) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="N19" t="str">
         <x:v>High</x:v>
@@ -1401,7 +1401,7 @@
         <x:v>Agent Assist and Next Best Action SME lead; data steward; technology owner</x:v>
       </x:c>
       <x:c r="M20" t="str">
-        <x:v>Named people and approval thresholds require client confirmation.</x:v>
+        <x:v>Validate Member service AI product team (record 15) against Agent Assist / Member Service evidence: stale knowledge article duplicates; confirm human-approved next-best-action workflow owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="N20" t="str">
         <x:v>Medium</x:v>
@@ -1445,7 +1445,7 @@
         <x:v>Unified Clinical and Claims Lakehouse SME lead; data steward; technology owner</x:v>
       </x:c>
       <x:c r="M21" t="str">
-        <x:v>Named people and approval thresholds require client confirmation.</x:v>
+        <x:v>Validate Clinical claims data product squad (record 16) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for org ownership.</x:v>
       </x:c>
       <x:c r="N21" t="str">
         <x:v>High</x:v>
@@ -1489,7 +1489,7 @@
         <x:v>IT Budget and Tower Baseline SME lead; data steward; technology owner</x:v>
       </x:c>
       <x:c r="M22" t="str">
-        <x:v>Named people and approval thresholds require client confirmation.</x:v>
+        <x:v>Confirm Technology finance office (record 17) current-vs-target status, module boundary, volume baseline, and relationship links before this org ownership record is used downstream.</x:v>
       </x:c>
       <x:c r="N22" t="str">
         <x:v>High</x:v>
@@ -1533,7 +1533,7 @@
         <x:v>Vendor and Contract Optimization SME lead; data steward; technology owner</x:v>
       </x:c>
       <x:c r="M23" t="str">
-        <x:v>Named people and approval thresholds require client confirmation.</x:v>
+        <x:v>Attach client evidence for Vendor management office (record 18), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="N23" t="str">
         <x:v>High</x:v>
@@ -1577,7 +1577,7 @@
         <x:v>Infrastructure and CMDB SME lead; data steward; technology owner</x:v>
       </x:c>
       <x:c r="M24" t="str">
-        <x:v>Named people and approval thresholds require client confirmation.</x:v>
+        <x:v>Reconcile Infrastructure operations team (record 19) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="N24" t="str">
         <x:v>High</x:v>
@@ -1621,7 +1621,7 @@
         <x:v>Incident Problem Change Operations SME lead; data steward; technology owner</x:v>
       </x:c>
       <x:c r="M25" t="str">
-        <x:v>Named people and approval thresholds require client confirmation.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for IT operations command center (record 20) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="N25" t="str">
         <x:v>Medium</x:v>
@@ -1639,7 +1639,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8ffb68225595440c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcd30ffa1f70b45a9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1714,7 +1714,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R000b17c39a3e421e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5ba4127e0ec24293"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1884,7 +1884,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf50d261d4e7347c5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R041b72af83ba4eec"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1938,7 +1938,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R84046a0a32ee4fde"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0424c805187d4266"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2048,7 +2048,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R77ac4faeb5c2488f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9a5bbd6dfd6845d6"/>
   </x:tableParts>
 </x:worksheet>
 </file>